--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100771</v>
+        <v>100781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100781</v>
+        <v>100782</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,7 +713,14 @@
           <t>20</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Björkåsakullen, Vg</t>
@@ -768,14 +775,30 @@
           <t>18:11</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Mycket osäker artbestämning.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog i branter</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Granskog i nordöstlig brant</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">

--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100782</v>
+        <v>100787</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100787</v>
+        <v>100790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100790</v>
+        <v>100796</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100796</v>
+        <v>100808</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100808</v>
+        <v>100809</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100809</v>
+        <v>100812</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 61372-2025 artfynd.xlsx
+++ b/artfynd/A 61372-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137293468</v>
       </c>
       <c r="B2" t="n">
-        <v>100812</v>
+        <v>100816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
